--- a/catalogos/cat_proc_sustitucion.xlsx
+++ b/catalogos/cat_proc_sustitucion.xlsx
@@ -29,17 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -60,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1870,14 +1864,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -4009,14 +4003,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -12756,14 +12750,14 @@
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13446,14 +13440,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14481,14 +14475,14 @@
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14688,14 +14682,14 @@
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -19555,14 +19549,14 @@
       <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K278" t="inlineStr"/>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -27219,32 +27213,24 @@
         <v>1</v>
       </c>
       <c r="E390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
           <t>BO_1974_01160,BO_1974_01415</t>
         </is>
       </c>
-      <c r="G390" s="2" t="inlineStr">
+      <c r="G390" t="inlineStr">
         <is>
           <t>TLP-3</t>
         </is>
       </c>
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
-      <c r="J390" t="inlineStr">
-        <is>
-          <t>TLP-3</t>
-        </is>
-      </c>
+      <c r="J390" t="inlineStr"/>
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr">
-        <is>
-          <t>TLP-3</t>
-        </is>
-      </c>
+      <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr"/>
@@ -27548,32 +27534,24 @@
         <v>1</v>
       </c>
       <c r="E395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
           <t>BO_1976_05604,BO_1977_02674</t>
         </is>
       </c>
-      <c r="G395" s="2" t="inlineStr">
+      <c r="G395" t="inlineStr">
         <is>
           <t>AH-VI</t>
         </is>
       </c>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr"/>
-      <c r="J395" t="inlineStr">
-        <is>
-          <t>AH-VI</t>
-        </is>
-      </c>
+      <c r="J395" t="inlineStr"/>
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
-      <c r="M395" t="inlineStr">
-        <is>
-          <t>AH-VI</t>
-        </is>
-      </c>
+      <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr"/>
       <c r="P395" t="inlineStr"/>
@@ -30653,32 +30631,24 @@
         <v>1</v>
       </c>
       <c r="E440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
           <t>BO_1974_02082</t>
         </is>
       </c>
-      <c r="G440" s="2" t="inlineStr">
+      <c r="G440" t="inlineStr">
         <is>
           <t>Ilegible</t>
         </is>
       </c>
       <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr"/>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>Ilegible</t>
-        </is>
-      </c>
+      <c r="J440" t="inlineStr"/>
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr"/>
-      <c r="M440" t="inlineStr">
-        <is>
-          <t>Ilegible</t>
-        </is>
-      </c>
+      <c r="M440" t="inlineStr"/>
       <c r="N440" t="inlineStr"/>
       <c r="O440" t="inlineStr"/>
       <c r="P440" t="inlineStr"/>
@@ -30860,7 +30830,7 @@
         <v>2</v>
       </c>
       <c r="E443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -30872,7 +30842,7 @@
           <t>HGRL</t>
         </is>
       </c>
-      <c r="H443" s="2" t="inlineStr">
+      <c r="H443" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
@@ -30883,15 +30853,11 @@
           <t>Hospital Ruben Leñero (Col Santo Tomas)</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
+      <c r="K443" t="inlineStr"/>
       <c r="L443" t="inlineStr"/>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Hospital Ruben Leñero (Col Santo Tomas)+MH</t>
+          <t>Hospital Ruben Leñero (Col Santo Tomas)</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31521,14 +31487,14 @@
         <v>2</v>
       </c>
       <c r="E452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
           <t>BO_1973_02802</t>
         </is>
       </c>
-      <c r="G452" s="2" t="inlineStr">
+      <c r="G452" t="inlineStr">
         <is>
           <t>BJ</t>
         </is>
@@ -31539,11 +31505,7 @@
         </is>
       </c>
       <c r="I452" t="inlineStr"/>
-      <c r="J452" t="inlineStr">
-        <is>
-          <t>BJ</t>
-        </is>
-      </c>
+      <c r="J452" t="inlineStr"/>
       <c r="K452" t="inlineStr">
         <is>
           <t>Coord Territorial 8 Cuauhtemoc (Col Obrera)</t>
@@ -31552,7 +31514,7 @@
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr">
         <is>
-          <t>BJ+Coord Territorial 8 Cuauhtemoc (Col Obrera)</t>
+          <t>Coord Territorial 8 Cuauhtemoc (Col Obrera)</t>
         </is>
       </c>
       <c r="N452" t="inlineStr"/>
@@ -32129,32 +32091,24 @@
         <v>1</v>
       </c>
       <c r="E460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
           <t>BO_1974_01693</t>
         </is>
       </c>
-      <c r="G460" s="2" t="inlineStr">
+      <c r="G460" t="inlineStr">
         <is>
           <t>3352</t>
         </is>
       </c>
       <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr"/>
-      <c r="J460" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
+      <c r="J460" t="inlineStr"/>
       <c r="K460" t="inlineStr"/>
       <c r="L460" t="inlineStr"/>
-      <c r="M460" t="inlineStr">
-        <is>
-          <t>3352</t>
-        </is>
-      </c>
+      <c r="M460" t="inlineStr"/>
       <c r="N460" t="inlineStr"/>
       <c r="O460" t="inlineStr"/>
       <c r="P460" t="inlineStr"/>
@@ -32182,32 +32136,24 @@
         <v>1</v>
       </c>
       <c r="E461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
           <t>BO_1980_03252</t>
         </is>
       </c>
-      <c r="G461" s="2" t="inlineStr">
+      <c r="G461" t="inlineStr">
         <is>
           <t>334</t>
         </is>
       </c>
       <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr"/>
-      <c r="J461" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
+      <c r="J461" t="inlineStr"/>
       <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
+      <c r="M461" t="inlineStr"/>
       <c r="N461" t="inlineStr"/>
       <c r="O461" t="inlineStr"/>
       <c r="P461" t="inlineStr"/>
@@ -32235,32 +32181,24 @@
         <v>1</v>
       </c>
       <c r="E462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
           <t>BO_1979_05210</t>
         </is>
       </c>
-      <c r="G462" s="2" t="inlineStr">
+      <c r="G462" t="inlineStr">
         <is>
           <t>332a</t>
         </is>
       </c>
       <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr"/>
-      <c r="J462" t="inlineStr">
-        <is>
-          <t>332a</t>
-        </is>
-      </c>
+      <c r="J462" t="inlineStr"/>
       <c r="K462" t="inlineStr"/>
       <c r="L462" t="inlineStr"/>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>332a</t>
-        </is>
-      </c>
+      <c r="M462" t="inlineStr"/>
       <c r="N462" t="inlineStr"/>
       <c r="O462" t="inlineStr"/>
       <c r="P462" t="inlineStr"/>
@@ -32373,32 +32311,24 @@
         <v>1</v>
       </c>
       <c r="E464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
           <t>BO_1973_05527</t>
         </is>
       </c>
-      <c r="G464" s="2" t="inlineStr">
+      <c r="G464" t="inlineStr">
         <is>
           <t>31032</t>
         </is>
       </c>
       <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr"/>
-      <c r="J464" t="inlineStr">
-        <is>
-          <t>31032</t>
-        </is>
-      </c>
+      <c r="J464" t="inlineStr"/>
       <c r="K464" t="inlineStr"/>
       <c r="L464" t="inlineStr"/>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>31032</t>
-        </is>
-      </c>
+      <c r="M464" t="inlineStr"/>
       <c r="N464" t="inlineStr"/>
       <c r="O464" t="inlineStr"/>
       <c r="P464" t="inlineStr"/>
@@ -32495,32 +32425,24 @@
         <v>1</v>
       </c>
       <c r="E466" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
           <t>BO_1978_04855</t>
         </is>
       </c>
-      <c r="G466" s="2" t="inlineStr">
+      <c r="G466" t="inlineStr">
         <is>
           <t>261a</t>
         </is>
       </c>
       <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr"/>
-      <c r="J466" t="inlineStr">
-        <is>
-          <t>261a</t>
-        </is>
-      </c>
+      <c r="J466" t="inlineStr"/>
       <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr"/>
-      <c r="M466" t="inlineStr">
-        <is>
-          <t>261a</t>
-        </is>
-      </c>
+      <c r="M466" t="inlineStr"/>
       <c r="N466" t="inlineStr"/>
       <c r="O466" t="inlineStr"/>
       <c r="P466" t="inlineStr"/>
@@ -33180,32 +33102,24 @@
         <v>1</v>
       </c>
       <c r="E475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
           <t>BO_1976_05212</t>
         </is>
       </c>
-      <c r="G475" s="2" t="inlineStr">
+      <c r="G475" t="inlineStr">
         <is>
           <t>HTL</t>
         </is>
       </c>
       <c r="H475" t="inlineStr"/>
       <c r="I475" t="inlineStr"/>
-      <c r="J475" t="inlineStr">
-        <is>
-          <t>HTL</t>
-        </is>
-      </c>
+      <c r="J475" t="inlineStr"/>
       <c r="K475" t="inlineStr"/>
       <c r="L475" t="inlineStr"/>
-      <c r="M475" t="inlineStr">
-        <is>
-          <t>HTL</t>
-        </is>
-      </c>
+      <c r="M475" t="inlineStr"/>
       <c r="N475" t="inlineStr"/>
       <c r="O475" t="inlineStr"/>
       <c r="P475" t="inlineStr"/>
@@ -33488,32 +33402,24 @@
         <v>1</v>
       </c>
       <c r="E479" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
           <t>BO_1975_04639</t>
         </is>
       </c>
-      <c r="G479" s="2" t="inlineStr">
+      <c r="G479" t="inlineStr">
         <is>
           <t>HM-1</t>
         </is>
       </c>
       <c r="H479" t="inlineStr"/>
       <c r="I479" t="inlineStr"/>
-      <c r="J479" t="inlineStr">
-        <is>
-          <t>HM-1</t>
-        </is>
-      </c>
+      <c r="J479" t="inlineStr"/>
       <c r="K479" t="inlineStr"/>
       <c r="L479" t="inlineStr"/>
-      <c r="M479" t="inlineStr">
-        <is>
-          <t>HM-1</t>
-        </is>
-      </c>
+      <c r="M479" t="inlineStr"/>
       <c r="N479" t="inlineStr"/>
       <c r="O479" t="inlineStr"/>
       <c r="P479" t="inlineStr"/>
@@ -33695,14 +33601,14 @@
         <v>2</v>
       </c>
       <c r="E482" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
           <t>BO_1973_05439</t>
         </is>
       </c>
-      <c r="G482" s="2" t="inlineStr">
+      <c r="G482" t="inlineStr">
         <is>
           <t>Hdz juarez</t>
         </is>
@@ -33713,11 +33619,7 @@
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
-      <c r="J482" t="inlineStr">
-        <is>
-          <t>Hdz juarez</t>
-        </is>
-      </c>
+      <c r="J482" t="inlineStr"/>
       <c r="K482" t="inlineStr">
         <is>
           <t>Coord Territorial 5 Iztapalapa (Col V Guerrero)</t>
@@ -33726,7 +33628,7 @@
       <c r="L482" t="inlineStr"/>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Coord Territorial 5 Iztapalapa (Col V Guerrero)+Hdz juarez</t>
+          <t>Coord Territorial 5 Iztapalapa (Col V Guerrero)</t>
         </is>
       </c>
       <c r="N482" t="inlineStr"/>
@@ -34287,32 +34189,24 @@
         <v>1</v>
       </c>
       <c r="E490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
           <t>BO_1979_04997</t>
         </is>
       </c>
-      <c r="G490" s="2" t="inlineStr">
+      <c r="G490" t="inlineStr">
         <is>
           <t>224a</t>
         </is>
       </c>
       <c r="H490" t="inlineStr"/>
       <c r="I490" t="inlineStr"/>
-      <c r="J490" t="inlineStr">
-        <is>
-          <t>224a</t>
-        </is>
-      </c>
+      <c r="J490" t="inlineStr"/>
       <c r="K490" t="inlineStr"/>
       <c r="L490" t="inlineStr"/>
-      <c r="M490" t="inlineStr">
-        <is>
-          <t>224a</t>
-        </is>
-      </c>
+      <c r="M490" t="inlineStr"/>
       <c r="N490" t="inlineStr"/>
       <c r="O490" t="inlineStr"/>
       <c r="P490" t="inlineStr"/>
@@ -34340,32 +34234,24 @@
         <v>1</v>
       </c>
       <c r="E491" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
           <t>BO_1981_02570</t>
         </is>
       </c>
-      <c r="G491" s="2" t="inlineStr">
+      <c r="G491" t="inlineStr">
         <is>
           <t>222</t>
         </is>
       </c>
       <c r="H491" t="inlineStr"/>
       <c r="I491" t="inlineStr"/>
-      <c r="J491" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+      <c r="J491" t="inlineStr"/>
       <c r="K491" t="inlineStr"/>
       <c r="L491" t="inlineStr"/>
-      <c r="M491" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
+      <c r="M491" t="inlineStr"/>
       <c r="N491" t="inlineStr"/>
       <c r="O491" t="inlineStr"/>
       <c r="P491" t="inlineStr"/>
@@ -35418,32 +35304,24 @@
         <v>1</v>
       </c>
       <c r="E505" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
           <t>BO_1969_03760</t>
         </is>
       </c>
-      <c r="G505" s="2" t="inlineStr">
+      <c r="G505" t="inlineStr">
         <is>
           <t>ISSSTE</t>
         </is>
       </c>
       <c r="H505" t="inlineStr"/>
       <c r="I505" t="inlineStr"/>
-      <c r="J505" t="inlineStr">
-        <is>
-          <t>ISSSTE</t>
-        </is>
-      </c>
+      <c r="J505" t="inlineStr"/>
       <c r="K505" t="inlineStr"/>
       <c r="L505" t="inlineStr"/>
-      <c r="M505" t="inlineStr">
-        <is>
-          <t>ISSSTE</t>
-        </is>
-      </c>
+      <c r="M505" t="inlineStr"/>
       <c r="N505" t="inlineStr"/>
       <c r="O505" t="inlineStr"/>
       <c r="P505" t="inlineStr"/>
@@ -35779,32 +35657,24 @@
         <v>1</v>
       </c>
       <c r="E510" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
           <t>BO_1981_07308</t>
         </is>
       </c>
-      <c r="G510" s="2" t="inlineStr">
+      <c r="G510" t="inlineStr">
         <is>
           <t>121</t>
         </is>
       </c>
       <c r="H510" t="inlineStr"/>
       <c r="I510" t="inlineStr"/>
-      <c r="J510" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
+      <c r="J510" t="inlineStr"/>
       <c r="K510" t="inlineStr"/>
       <c r="L510" t="inlineStr"/>
-      <c r="M510" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
+      <c r="M510" t="inlineStr"/>
       <c r="N510" t="inlineStr"/>
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr"/>
@@ -35832,32 +35702,24 @@
         <v>1</v>
       </c>
       <c r="E511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
           <t>BO_1977_01340</t>
         </is>
       </c>
-      <c r="G511" s="2" t="inlineStr">
+      <c r="G511" t="inlineStr">
         <is>
           <t>120-I</t>
         </is>
       </c>
       <c r="H511" t="inlineStr"/>
       <c r="I511" t="inlineStr"/>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>120-I</t>
-        </is>
-      </c>
+      <c r="J511" t="inlineStr"/>
       <c r="K511" t="inlineStr"/>
       <c r="L511" t="inlineStr"/>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>120-I</t>
-        </is>
-      </c>
+      <c r="M511" t="inlineStr"/>
       <c r="N511" t="inlineStr"/>
       <c r="O511" t="inlineStr"/>
       <c r="P511" t="inlineStr"/>
@@ -36230,14 +36092,14 @@
         <v>2</v>
       </c>
       <c r="E517" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
           <t>BO_1971_02174</t>
         </is>
       </c>
-      <c r="G517" s="2" t="inlineStr">
+      <c r="G517" t="inlineStr">
         <is>
           <t>DP</t>
         </is>
@@ -36248,11 +36110,7 @@
         </is>
       </c>
       <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t>DP</t>
-        </is>
-      </c>
+      <c r="J517" t="inlineStr"/>
       <c r="K517" t="inlineStr">
         <is>
           <t>Coord Territorial 1 Tlalpan (Col Ampliacion Miguel Hidalgo)</t>
@@ -36261,7 +36119,7 @@
       <c r="L517" t="inlineStr"/>
       <c r="M517" t="inlineStr">
         <is>
-          <t>Coord Territorial 1 Tlalpan (Col Ampliacion Miguel Hidalgo)+DP</t>
+          <t>Coord Territorial 1 Tlalpan (Col Ampliacion Miguel Hidalgo)</t>
         </is>
       </c>
       <c r="N517" t="inlineStr"/>
@@ -37310,32 +37168,24 @@
         <v>1</v>
       </c>
       <c r="E533" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
           <t>BO_1975_03690</t>
         </is>
       </c>
-      <c r="G533" s="2" t="inlineStr">
+      <c r="G533" t="inlineStr">
         <is>
           <t>VH-1</t>
         </is>
       </c>
       <c r="H533" t="inlineStr"/>
       <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr">
-        <is>
-          <t>VH-1</t>
-        </is>
-      </c>
+      <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr"/>
-      <c r="M533" t="inlineStr">
-        <is>
-          <t>VH-1</t>
-        </is>
-      </c>
+      <c r="M533" t="inlineStr"/>
       <c r="N533" t="inlineStr"/>
       <c r="O533" t="inlineStr"/>
       <c r="P533" t="inlineStr"/>
@@ -37363,14 +37213,14 @@
         <v>2</v>
       </c>
       <c r="E534" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
           <t>BO_1977_04749</t>
         </is>
       </c>
-      <c r="G534" s="2" t="inlineStr">
+      <c r="G534" t="inlineStr">
         <is>
           <t>M-13</t>
         </is>
@@ -37381,11 +37231,7 @@
         </is>
       </c>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr">
-        <is>
-          <t>M-13</t>
-        </is>
-      </c>
+      <c r="J534" t="inlineStr"/>
       <c r="K534" t="inlineStr">
         <is>
           <t>Procuraduria General de la Republica</t>
@@ -37394,7 +37240,7 @@
       <c r="L534" t="inlineStr"/>
       <c r="M534" t="inlineStr">
         <is>
-          <t>M-13+Procuraduria General de la Republica</t>
+          <t>Procuraduria General de la Republica</t>
         </is>
       </c>
       <c r="N534" t="inlineStr"/>
@@ -37517,32 +37363,24 @@
         <v>1</v>
       </c>
       <c r="E536" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
           <t>BO_1980_01642</t>
         </is>
       </c>
-      <c r="G536" s="2" t="inlineStr">
+      <c r="G536" t="inlineStr">
         <is>
           <t>1687</t>
         </is>
       </c>
       <c r="H536" t="inlineStr"/>
       <c r="I536" t="inlineStr"/>
-      <c r="J536" t="inlineStr">
-        <is>
-          <t>1687</t>
-        </is>
-      </c>
+      <c r="J536" t="inlineStr"/>
       <c r="K536" t="inlineStr"/>
       <c r="L536" t="inlineStr"/>
-      <c r="M536" t="inlineStr">
-        <is>
-          <t>1687</t>
-        </is>
-      </c>
+      <c r="M536" t="inlineStr"/>
       <c r="N536" t="inlineStr"/>
       <c r="O536" t="inlineStr"/>
       <c r="P536" t="inlineStr"/>
@@ -39367,32 +39205,24 @@
         <v>1</v>
       </c>
       <c r="E562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
           <t>BO_1981_04224</t>
         </is>
       </c>
-      <c r="G562" s="2" t="inlineStr">
+      <c r="G562" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
       <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
+      <c r="J562" t="inlineStr"/>
       <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr"/>
-      <c r="M562" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
+      <c r="M562" t="inlineStr"/>
       <c r="N562" t="inlineStr"/>
       <c r="O562" t="inlineStr"/>
       <c r="P562" t="inlineStr"/>
@@ -39850,32 +39680,24 @@
         <v>1</v>
       </c>
       <c r="E569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
           <t>BO_1977_01645</t>
         </is>
       </c>
-      <c r="G569" s="2" t="inlineStr">
+      <c r="G569" t="inlineStr">
         <is>
           <t>MH-6</t>
         </is>
       </c>
       <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr">
-        <is>
-          <t>MH-6</t>
-        </is>
-      </c>
+      <c r="J569" t="inlineStr"/>
       <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr"/>
-      <c r="M569" t="inlineStr">
-        <is>
-          <t>MH-6</t>
-        </is>
-      </c>
+      <c r="M569" t="inlineStr"/>
       <c r="N569" t="inlineStr"/>
       <c r="O569" t="inlineStr"/>
       <c r="P569" t="inlineStr"/>
@@ -39903,7 +39725,7 @@
         <v>2</v>
       </c>
       <c r="E570" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -39915,7 +39737,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="H570" s="2" t="inlineStr">
+      <c r="H570" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
@@ -39926,15 +39748,11 @@
           <t>Hospital Balbuena (Col Jardin Balbuena)</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
+      <c r="K570" t="inlineStr"/>
       <c r="L570" t="inlineStr"/>
       <c r="M570" t="inlineStr">
         <is>
-          <t>Hospital Balbuena (Col Jardin Balbuena)+MH</t>
+          <t>Hospital Balbuena (Col Jardin Balbuena)</t>
         </is>
       </c>
       <c r="N570" t="inlineStr">
@@ -40341,32 +40159,24 @@
         <v>1</v>
       </c>
       <c r="E576" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
           <t>BO_1973_03520</t>
         </is>
       </c>
-      <c r="G576" s="2" t="inlineStr">
+      <c r="G576" t="inlineStr">
         <is>
           <t>M.A.</t>
         </is>
       </c>
       <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr">
-        <is>
-          <t>M.A.</t>
-        </is>
-      </c>
+      <c r="J576" t="inlineStr"/>
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr"/>
-      <c r="M576" t="inlineStr">
-        <is>
-          <t>M.A.</t>
-        </is>
-      </c>
+      <c r="M576" t="inlineStr"/>
       <c r="N576" t="inlineStr"/>
       <c r="O576" t="inlineStr"/>
       <c r="P576" t="inlineStr"/>
@@ -40617,32 +40427,24 @@
         <v>1</v>
       </c>
       <c r="E580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
           <t>BO_1978_00535</t>
         </is>
       </c>
-      <c r="G580" s="2" t="inlineStr">
+      <c r="G580" t="inlineStr">
         <is>
           <t>24a 282</t>
         </is>
       </c>
       <c r="H580" t="inlineStr"/>
       <c r="I580" t="inlineStr"/>
-      <c r="J580" t="inlineStr">
-        <is>
-          <t>24a 282</t>
-        </is>
-      </c>
+      <c r="J580" t="inlineStr"/>
       <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr"/>
-      <c r="M580" t="inlineStr">
-        <is>
-          <t>24a 282</t>
-        </is>
-      </c>
+      <c r="M580" t="inlineStr"/>
       <c r="N580" t="inlineStr"/>
       <c r="O580" t="inlineStr"/>
       <c r="P580" t="inlineStr"/>
@@ -41456,32 +41258,24 @@
         <v>1</v>
       </c>
       <c r="E591" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
           <t>BO_1977_01474</t>
         </is>
       </c>
-      <c r="G591" s="2" t="inlineStr">
+      <c r="G591" t="inlineStr">
         <is>
           <t>MH</t>
         </is>
       </c>
       <c r="H591" t="inlineStr"/>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
+      <c r="J591" t="inlineStr"/>
       <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr"/>
-      <c r="M591" t="inlineStr">
-        <is>
-          <t>MH</t>
-        </is>
-      </c>
+      <c r="M591" t="inlineStr"/>
       <c r="N591" t="inlineStr"/>
       <c r="O591" t="inlineStr"/>
       <c r="P591" t="inlineStr"/>
@@ -41578,32 +41372,24 @@
         <v>1</v>
       </c>
       <c r="E593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
           <t>BO_1976_03162</t>
         </is>
       </c>
-      <c r="G593" s="2" t="inlineStr">
+      <c r="G593" t="inlineStr">
         <is>
           <t>TEX</t>
         </is>
       </c>
       <c r="H593" t="inlineStr"/>
       <c r="I593" t="inlineStr"/>
-      <c r="J593" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
+      <c r="J593" t="inlineStr"/>
       <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr"/>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
+      <c r="M593" t="inlineStr"/>
       <c r="N593" t="inlineStr"/>
       <c r="O593" t="inlineStr"/>
       <c r="P593" t="inlineStr"/>
@@ -41700,32 +41486,24 @@
         <v>1</v>
       </c>
       <c r="E595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
           <t>BO_1976_05305</t>
         </is>
       </c>
-      <c r="G595" s="2" t="inlineStr">
+      <c r="G595" t="inlineStr">
         <is>
           <t>TC-2</t>
         </is>
       </c>
       <c r="H595" t="inlineStr"/>
       <c r="I595" t="inlineStr"/>
-      <c r="J595" t="inlineStr">
-        <is>
-          <t>TC-2</t>
-        </is>
-      </c>
+      <c r="J595" t="inlineStr"/>
       <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr"/>
-      <c r="M595" t="inlineStr">
-        <is>
-          <t>TC-2</t>
-        </is>
-      </c>
+      <c r="M595" t="inlineStr"/>
       <c r="N595" t="inlineStr"/>
       <c r="O595" t="inlineStr"/>
       <c r="P595" t="inlineStr"/>
@@ -41838,7 +41616,7 @@
         <v>2</v>
       </c>
       <c r="E597" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -41850,7 +41628,7 @@
           <t>HCMS21</t>
         </is>
       </c>
-      <c r="H597" s="2" t="inlineStr">
+      <c r="H597" t="inlineStr">
         <is>
           <t>MJ</t>
         </is>
@@ -41861,15 +41639,11 @@
           <t>Hospital Centro Médico Nacional Siglo XXI (Col Doctores)</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
+      <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
-          <t>Hospital Centro Médico Nacional Siglo XXI (Col Doctores)+MJ</t>
+          <t>Hospital Centro Médico Nacional Siglo XXI (Col Doctores)</t>
         </is>
       </c>
       <c r="N597" t="inlineStr">
@@ -41915,32 +41689,24 @@
         <v>1</v>
       </c>
       <c r="E598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
           <t>BO_1975_02506</t>
         </is>
       </c>
-      <c r="G598" s="2" t="inlineStr">
+      <c r="G598" t="inlineStr">
         <is>
           <t>MJ-3</t>
         </is>
       </c>
       <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr"/>
-      <c r="J598" t="inlineStr">
-        <is>
-          <t>MJ-3</t>
-        </is>
-      </c>
+      <c r="J598" t="inlineStr"/>
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr"/>
-      <c r="M598" t="inlineStr">
-        <is>
-          <t>MJ-3</t>
-        </is>
-      </c>
+      <c r="M598" t="inlineStr"/>
       <c r="N598" t="inlineStr"/>
       <c r="O598" t="inlineStr"/>
       <c r="P598" t="inlineStr"/>
@@ -41968,32 +41734,24 @@
         <v>1</v>
       </c>
       <c r="E599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
           <t>BO_1975_01557</t>
         </is>
       </c>
-      <c r="G599" s="2" t="inlineStr">
+      <c r="G599" t="inlineStr">
         <is>
           <t>MHRC</t>
         </is>
       </c>
       <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr"/>
-      <c r="J599" t="inlineStr">
-        <is>
-          <t>MHRC</t>
-        </is>
-      </c>
+      <c r="J599" t="inlineStr"/>
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr"/>
-      <c r="M599" t="inlineStr">
-        <is>
-          <t>MHRC</t>
-        </is>
-      </c>
+      <c r="M599" t="inlineStr"/>
       <c r="N599" t="inlineStr"/>
       <c r="O599" t="inlineStr"/>
       <c r="P599" t="inlineStr"/>
@@ -42467,32 +42225,24 @@
         <v>1</v>
       </c>
       <c r="E606" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
           <t>BO_1973_01422</t>
         </is>
       </c>
-      <c r="G606" s="2" t="inlineStr">
+      <c r="G606" t="inlineStr">
         <is>
           <t>N.O.</t>
         </is>
       </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr"/>
-      <c r="J606" t="inlineStr">
-        <is>
-          <t>N.O.</t>
-        </is>
-      </c>
+      <c r="J606" t="inlineStr"/>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr"/>
-      <c r="M606" t="inlineStr">
-        <is>
-          <t>N.O.</t>
-        </is>
-      </c>
+      <c r="M606" t="inlineStr"/>
       <c r="N606" t="inlineStr"/>
       <c r="O606" t="inlineStr"/>
       <c r="P606" t="inlineStr"/>
@@ -42520,32 +42270,24 @@
         <v>1</v>
       </c>
       <c r="E607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
           <t>BO_1975_02878</t>
         </is>
       </c>
-      <c r="G607" s="2" t="inlineStr">
+      <c r="G607" t="inlineStr">
         <is>
           <t>T-1</t>
         </is>
       </c>
       <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr"/>
-      <c r="J607" t="inlineStr">
-        <is>
-          <t>T-1</t>
-        </is>
-      </c>
+      <c r="J607" t="inlineStr"/>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr"/>
-      <c r="M607" t="inlineStr">
-        <is>
-          <t>T-1</t>
-        </is>
-      </c>
+      <c r="M607" t="inlineStr"/>
       <c r="N607" t="inlineStr"/>
       <c r="O607" t="inlineStr"/>
       <c r="P607" t="inlineStr"/>
@@ -42573,32 +42315,24 @@
         <v>1</v>
       </c>
       <c r="E608" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
           <t>BO_1974_04430</t>
         </is>
       </c>
-      <c r="G608" s="2" t="inlineStr">
+      <c r="G608" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
       <c r="H608" t="inlineStr"/>
       <c r="I608" t="inlineStr"/>
-      <c r="J608" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+      <c r="J608" t="inlineStr"/>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr"/>
-      <c r="M608" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
+      <c r="M608" t="inlineStr"/>
       <c r="N608" t="inlineStr"/>
       <c r="O608" t="inlineStr"/>
       <c r="P608" t="inlineStr"/>
@@ -42963,32 +42697,24 @@
         <v>1</v>
       </c>
       <c r="E614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
           <t>BO_1976_06268</t>
         </is>
       </c>
-      <c r="G614" s="2" t="inlineStr">
+      <c r="G614" t="inlineStr">
         <is>
           <t>PP</t>
         </is>
       </c>
       <c r="H614" t="inlineStr"/>
       <c r="I614" t="inlineStr"/>
-      <c r="J614" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
+      <c r="J614" t="inlineStr"/>
       <c r="K614" t="inlineStr"/>
       <c r="L614" t="inlineStr"/>
-      <c r="M614" t="inlineStr">
-        <is>
-          <t>PP</t>
-        </is>
-      </c>
+      <c r="M614" t="inlineStr"/>
       <c r="N614" t="inlineStr"/>
       <c r="O614" t="inlineStr"/>
       <c r="P614" t="inlineStr"/>
@@ -43223,32 +42949,24 @@
         <v>1</v>
       </c>
       <c r="E618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
           <t>BO_1977_05091</t>
         </is>
       </c>
-      <c r="G618" s="2" t="inlineStr">
+      <c r="G618" t="inlineStr">
         <is>
           <t>NJ Edo Mex</t>
         </is>
       </c>
       <c r="H618" t="inlineStr"/>
       <c r="I618" t="inlineStr"/>
-      <c r="J618" t="inlineStr">
-        <is>
-          <t>NJ Edo Mex</t>
-        </is>
-      </c>
+      <c r="J618" t="inlineStr"/>
       <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr"/>
-      <c r="M618" t="inlineStr">
-        <is>
-          <t>NJ Edo Mex</t>
-        </is>
-      </c>
+      <c r="M618" t="inlineStr"/>
       <c r="N618" t="inlineStr"/>
       <c r="O618" t="inlineStr"/>
       <c r="P618" t="inlineStr"/>
@@ -43276,32 +42994,24 @@
         <v>1</v>
       </c>
       <c r="E619" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
           <t>BO_1978_01084</t>
         </is>
       </c>
-      <c r="G619" s="2" t="inlineStr">
+      <c r="G619" t="inlineStr">
         <is>
           <t>NJ</t>
         </is>
       </c>
       <c r="H619" t="inlineStr"/>
       <c r="I619" t="inlineStr"/>
-      <c r="J619" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
+      <c r="J619" t="inlineStr"/>
       <c r="K619" t="inlineStr"/>
       <c r="L619" t="inlineStr"/>
-      <c r="M619" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
+      <c r="M619" t="inlineStr"/>
       <c r="N619" t="inlineStr"/>
       <c r="O619" t="inlineStr"/>
       <c r="P619" t="inlineStr"/>
@@ -43329,32 +43039,24 @@
         <v>1</v>
       </c>
       <c r="E620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
           <t>BO_1977_01767</t>
         </is>
       </c>
-      <c r="G620" s="2" t="inlineStr">
+      <c r="G620" t="inlineStr">
         <is>
           <t>NH-II</t>
         </is>
       </c>
       <c r="H620" t="inlineStr"/>
       <c r="I620" t="inlineStr"/>
-      <c r="J620" t="inlineStr">
-        <is>
-          <t>NH-II</t>
-        </is>
-      </c>
+      <c r="J620" t="inlineStr"/>
       <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr"/>
-      <c r="M620" t="inlineStr">
-        <is>
-          <t>NH-II</t>
-        </is>
-      </c>
+      <c r="M620" t="inlineStr"/>
       <c r="N620" t="inlineStr"/>
       <c r="O620" t="inlineStr"/>
       <c r="P620" t="inlineStr"/>
@@ -43536,14 +43238,14 @@
         <v>2</v>
       </c>
       <c r="E623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
           <t>BO_1971_00924</t>
         </is>
       </c>
-      <c r="G623" s="2" t="inlineStr">
+      <c r="G623" t="inlineStr">
         <is>
           <t>CRN</t>
         </is>
@@ -43554,11 +43256,7 @@
         </is>
       </c>
       <c r="I623" t="inlineStr"/>
-      <c r="J623" t="inlineStr">
-        <is>
-          <t>CRN</t>
-        </is>
-      </c>
+      <c r="J623" t="inlineStr"/>
       <c r="K623" t="inlineStr">
         <is>
           <t>Coord Territorial 1 Venustiano Carranza (Col Merced)</t>
@@ -43567,7 +43265,7 @@
       <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr">
         <is>
-          <t>CRN+Coord Territorial 1 Venustiano Carranza (Col Merced)</t>
+          <t>Coord Territorial 1 Venustiano Carranza (Col Merced)</t>
         </is>
       </c>
       <c r="N623" t="inlineStr"/>
@@ -43613,32 +43311,24 @@
         <v>1</v>
       </c>
       <c r="E624" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
           <t>BO_1971_01331</t>
         </is>
       </c>
-      <c r="G624" s="2" t="inlineStr">
+      <c r="G624" t="inlineStr">
         <is>
           <t>C. R. Cela</t>
         </is>
       </c>
       <c r="H624" t="inlineStr"/>
       <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr">
-        <is>
-          <t>C. R. Cela</t>
-        </is>
-      </c>
+      <c r="J624" t="inlineStr"/>
       <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr"/>
-      <c r="M624" t="inlineStr">
-        <is>
-          <t>C. R. Cela</t>
-        </is>
-      </c>
+      <c r="M624" t="inlineStr"/>
       <c r="N624" t="inlineStr"/>
       <c r="O624" t="inlineStr"/>
       <c r="P624" t="inlineStr"/>
@@ -43735,32 +43425,24 @@
         <v>1</v>
       </c>
       <c r="E626" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
           <t>BO_1975_04183</t>
         </is>
       </c>
-      <c r="G626" s="2" t="inlineStr">
+      <c r="G626" t="inlineStr">
         <is>
           <t>C-2</t>
         </is>
       </c>
       <c r="H626" t="inlineStr"/>
       <c r="I626" t="inlineStr"/>
-      <c r="J626" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
+      <c r="J626" t="inlineStr"/>
       <c r="K626" t="inlineStr"/>
       <c r="L626" t="inlineStr"/>
-      <c r="M626" t="inlineStr">
-        <is>
-          <t>C-2</t>
-        </is>
-      </c>
+      <c r="M626" t="inlineStr"/>
       <c r="N626" t="inlineStr"/>
       <c r="O626" t="inlineStr"/>
       <c r="P626" t="inlineStr"/>
@@ -44043,32 +43725,24 @@
         <v>1</v>
       </c>
       <c r="E630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
           <t>BO_1980_03281</t>
         </is>
       </c>
-      <c r="G630" s="2" t="inlineStr">
+      <c r="G630" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
       <c r="H630" t="inlineStr"/>
       <c r="I630" t="inlineStr"/>
-      <c r="J630" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="J630" t="inlineStr"/>
       <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr"/>
-      <c r="M630" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
+      <c r="M630" t="inlineStr"/>
       <c r="N630" t="inlineStr"/>
       <c r="O630" t="inlineStr"/>
       <c r="P630" t="inlineStr"/>
@@ -44096,32 +43770,24 @@
         <v>1</v>
       </c>
       <c r="E631" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
           <t>BO_1977_05965</t>
         </is>
       </c>
-      <c r="G631" s="2" t="inlineStr">
+      <c r="G631" t="inlineStr">
         <is>
           <t>AO-2</t>
         </is>
       </c>
       <c r="H631" t="inlineStr"/>
       <c r="I631" t="inlineStr"/>
-      <c r="J631" t="inlineStr">
-        <is>
-          <t>AO-2</t>
-        </is>
-      </c>
+      <c r="J631" t="inlineStr"/>
       <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr"/>
-      <c r="M631" t="inlineStr">
-        <is>
-          <t>AO-2</t>
-        </is>
-      </c>
+      <c r="M631" t="inlineStr"/>
       <c r="N631" t="inlineStr"/>
       <c r="O631" t="inlineStr"/>
       <c r="P631" t="inlineStr"/>
@@ -45869,14 +45535,14 @@
         <v>2</v>
       </c>
       <c r="E656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
           <t>BO_1975_03799</t>
         </is>
       </c>
-      <c r="G656" s="2" t="inlineStr">
+      <c r="G656" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
@@ -45887,11 +45553,7 @@
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
-      <c r="J656" t="inlineStr">
-        <is>
-          <t>CD</t>
-        </is>
-      </c>
+      <c r="J656" t="inlineStr"/>
       <c r="K656" t="inlineStr">
         <is>
           <t>Cruz Roja (Col Polanco)</t>
@@ -45900,7 +45562,7 @@
       <c r="L656" t="inlineStr"/>
       <c r="M656" t="inlineStr">
         <is>
-          <t>CD+Cruz Roja (Col Polanco)</t>
+          <t>Cruz Roja (Col Polanco)</t>
         </is>
       </c>
       <c r="N656" t="inlineStr"/>
@@ -46015,32 +45677,24 @@
         <v>1</v>
       </c>
       <c r="E658" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
           <t>BO_1975_01317</t>
         </is>
       </c>
-      <c r="G658" s="2" t="inlineStr">
+      <c r="G658" t="inlineStr">
         <is>
           <t>C-X-1</t>
         </is>
       </c>
       <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr"/>
-      <c r="J658" t="inlineStr">
-        <is>
-          <t>C-X-1</t>
-        </is>
-      </c>
+      <c r="J658" t="inlineStr"/>
       <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr"/>
-      <c r="M658" t="inlineStr">
-        <is>
-          <t>C-X-1</t>
-        </is>
-      </c>
+      <c r="M658" t="inlineStr"/>
       <c r="N658" t="inlineStr"/>
       <c r="O658" t="inlineStr"/>
       <c r="P658" t="inlineStr"/>
@@ -46153,32 +45807,24 @@
         <v>1</v>
       </c>
       <c r="E660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
           <t>BO_1981_04376</t>
         </is>
       </c>
-      <c r="G660" s="2" t="inlineStr">
+      <c r="G660" t="inlineStr">
         <is>
           <t>79</t>
         </is>
       </c>
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr"/>
-      <c r="J660" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="J660" t="inlineStr"/>
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr"/>
-      <c r="M660" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
+      <c r="M660" t="inlineStr"/>
       <c r="N660" t="inlineStr"/>
       <c r="O660" t="inlineStr"/>
       <c r="P660" t="inlineStr"/>
@@ -46206,32 +45852,24 @@
         <v>1</v>
       </c>
       <c r="E661" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
           <t>BO_1979_04218</t>
         </is>
       </c>
-      <c r="G661" s="2" t="inlineStr">
+      <c r="G661" t="inlineStr">
         <is>
           <t>78a</t>
         </is>
       </c>
       <c r="H661" t="inlineStr"/>
       <c r="I661" t="inlineStr"/>
-      <c r="J661" t="inlineStr">
-        <is>
-          <t>78a</t>
-        </is>
-      </c>
+      <c r="J661" t="inlineStr"/>
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr"/>
-      <c r="M661" t="inlineStr">
-        <is>
-          <t>78a</t>
-        </is>
-      </c>
+      <c r="M661" t="inlineStr"/>
       <c r="N661" t="inlineStr"/>
       <c r="O661" t="inlineStr"/>
       <c r="P661" t="inlineStr"/>
@@ -46259,32 +45897,24 @@
         <v>1</v>
       </c>
       <c r="E662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
           <t>BO_1980_02879</t>
         </is>
       </c>
-      <c r="G662" s="2" t="inlineStr">
+      <c r="G662" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
       <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr"/>
-      <c r="J662" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+      <c r="J662" t="inlineStr"/>
       <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr"/>
-      <c r="M662" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
+      <c r="M662" t="inlineStr"/>
       <c r="N662" t="inlineStr"/>
       <c r="O662" t="inlineStr"/>
       <c r="P662" t="inlineStr"/>
@@ -46312,32 +45942,24 @@
         <v>1</v>
       </c>
       <c r="E663" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
           <t>BO_1981_05182</t>
         </is>
       </c>
-      <c r="G663" s="2" t="inlineStr">
+      <c r="G663" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr"/>
-      <c r="J663" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="J663" t="inlineStr"/>
       <c r="K663" t="inlineStr"/>
       <c r="L663" t="inlineStr"/>
-      <c r="M663" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="M663" t="inlineStr"/>
       <c r="N663" t="inlineStr"/>
       <c r="O663" t="inlineStr"/>
       <c r="P663" t="inlineStr"/>
@@ -46365,32 +45987,24 @@
         <v>1</v>
       </c>
       <c r="E664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
           <t>BO_1977_04403</t>
         </is>
       </c>
-      <c r="G664" s="2" t="inlineStr">
+      <c r="G664" t="inlineStr">
         <is>
           <t>73a</t>
         </is>
       </c>
       <c r="H664" t="inlineStr"/>
       <c r="I664" t="inlineStr"/>
-      <c r="J664" t="inlineStr">
-        <is>
-          <t>73a</t>
-        </is>
-      </c>
+      <c r="J664" t="inlineStr"/>
       <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr"/>
-      <c r="M664" t="inlineStr">
-        <is>
-          <t>73a</t>
-        </is>
-      </c>
+      <c r="M664" t="inlineStr"/>
       <c r="N664" t="inlineStr"/>
       <c r="O664" t="inlineStr"/>
       <c r="P664" t="inlineStr"/>
@@ -46694,32 +46308,24 @@
         <v>1</v>
       </c>
       <c r="E669" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
           <t>BO_1981_02073</t>
         </is>
       </c>
-      <c r="G669" s="2" t="inlineStr">
+      <c r="G669" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
       <c r="H669" t="inlineStr"/>
       <c r="I669" t="inlineStr"/>
-      <c r="J669" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+      <c r="J669" t="inlineStr"/>
       <c r="K669" t="inlineStr"/>
       <c r="L669" t="inlineStr"/>
-      <c r="M669" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
+      <c r="M669" t="inlineStr"/>
       <c r="N669" t="inlineStr"/>
       <c r="O669" t="inlineStr"/>
       <c r="P669" t="inlineStr"/>
@@ -46885,32 +46491,24 @@
         <v>1</v>
       </c>
       <c r="E672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
           <t>BO_1977_01720</t>
         </is>
       </c>
-      <c r="G672" s="2" t="inlineStr">
+      <c r="G672" t="inlineStr">
         <is>
           <t>CA-6</t>
         </is>
       </c>
       <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr"/>
-      <c r="J672" t="inlineStr">
-        <is>
-          <t>CA-6</t>
-        </is>
-      </c>
+      <c r="J672" t="inlineStr"/>
       <c r="K672" t="inlineStr"/>
       <c r="L672" t="inlineStr"/>
-      <c r="M672" t="inlineStr">
-        <is>
-          <t>CA-6</t>
-        </is>
-      </c>
+      <c r="M672" t="inlineStr"/>
       <c r="N672" t="inlineStr"/>
       <c r="O672" t="inlineStr"/>
       <c r="P672" t="inlineStr"/>
@@ -47947,7 +47545,7 @@
         <v>2</v>
       </c>
       <c r="E686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -47959,7 +47557,7 @@
           <t>BJ-1</t>
         </is>
       </c>
-      <c r="H686" s="2" t="inlineStr">
+      <c r="H686" t="inlineStr">
         <is>
           <t>C-CV</t>
         </is>
@@ -47970,15 +47568,11 @@
           <t>Coord Territorial 1 Benito Juarez (Col Santa Cruz Atoyac)</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr">
-        <is>
-          <t>C-CV</t>
-        </is>
-      </c>
+      <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr"/>
       <c r="M686" t="inlineStr">
         <is>
-          <t>C-CV+Coord Territorial 1 Benito Juarez (Col Santa Cruz Atoyac)</t>
+          <t>Coord Territorial 1 Benito Juarez (Col Santa Cruz Atoyac)</t>
         </is>
       </c>
       <c r="N686" t="inlineStr">
@@ -48929,32 +48523,24 @@
         <v>1</v>
       </c>
       <c r="E700" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
           <t>BO_1978_01190</t>
         </is>
       </c>
-      <c r="G700" s="2" t="inlineStr">
+      <c r="G700" t="inlineStr">
         <is>
           <t>115a</t>
         </is>
       </c>
       <c r="H700" t="inlineStr"/>
       <c r="I700" t="inlineStr"/>
-      <c r="J700" t="inlineStr">
-        <is>
-          <t>115a</t>
-        </is>
-      </c>
+      <c r="J700" t="inlineStr"/>
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr"/>
-      <c r="M700" t="inlineStr">
-        <is>
-          <t>115a</t>
-        </is>
-      </c>
+      <c r="M700" t="inlineStr"/>
       <c r="N700" t="inlineStr"/>
       <c r="O700" t="inlineStr"/>
       <c r="P700" t="inlineStr"/>
@@ -48982,32 +48568,24 @@
         <v>1</v>
       </c>
       <c r="E701" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
           <t>BO_1973_01635</t>
         </is>
       </c>
-      <c r="G701" s="2" t="inlineStr">
+      <c r="G701" t="inlineStr">
         <is>
           <t>1136</t>
         </is>
       </c>
       <c r="H701" t="inlineStr"/>
       <c r="I701" t="inlineStr"/>
-      <c r="J701" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
+      <c r="J701" t="inlineStr"/>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr"/>
-      <c r="M701" t="inlineStr">
-        <is>
-          <t>1136</t>
-        </is>
-      </c>
+      <c r="M701" t="inlineStr"/>
       <c r="N701" t="inlineStr"/>
       <c r="O701" t="inlineStr"/>
       <c r="P701" t="inlineStr"/>
@@ -49943,32 +49521,24 @@
         <v>1</v>
       </c>
       <c r="E714" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
           <t>BO_1976_06416</t>
         </is>
       </c>
-      <c r="G714" s="2" t="inlineStr">
+      <c r="G714" t="inlineStr">
         <is>
           <t>C-A</t>
         </is>
       </c>
       <c r="H714" t="inlineStr"/>
       <c r="I714" t="inlineStr"/>
-      <c r="J714" t="inlineStr">
-        <is>
-          <t>C-A</t>
-        </is>
-      </c>
+      <c r="J714" t="inlineStr"/>
       <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr"/>
-      <c r="M714" t="inlineStr">
-        <is>
-          <t>C-A</t>
-        </is>
-      </c>
+      <c r="M714" t="inlineStr"/>
       <c r="N714" t="inlineStr"/>
       <c r="O714" t="inlineStr"/>
       <c r="P714" t="inlineStr"/>
@@ -50612,32 +50182,24 @@
         <v>1</v>
       </c>
       <c r="E723" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
           <t>BO_1975_05458</t>
         </is>
       </c>
-      <c r="G723" s="2" t="inlineStr">
+      <c r="G723" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr"/>
-      <c r="J723" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J723" t="inlineStr"/>
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr"/>
-      <c r="M723" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M723" t="inlineStr"/>
       <c r="N723" t="inlineStr"/>
       <c r="O723" t="inlineStr"/>
       <c r="P723" t="inlineStr"/>
@@ -51355,32 +50917,24 @@
         <v>1</v>
       </c>
       <c r="E734" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
           <t>BO_1976_00280</t>
         </is>
       </c>
-      <c r="G734" s="2" t="inlineStr">
+      <c r="G734" t="inlineStr">
         <is>
           <t>AZ-2</t>
         </is>
       </c>
       <c r="H734" t="inlineStr"/>
       <c r="I734" t="inlineStr"/>
-      <c r="J734" t="inlineStr">
-        <is>
-          <t>AZ-2</t>
-        </is>
-      </c>
+      <c r="J734" t="inlineStr"/>
       <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr"/>
-      <c r="M734" t="inlineStr">
-        <is>
-          <t>AZ-2</t>
-        </is>
-      </c>
+      <c r="M734" t="inlineStr"/>
       <c r="N734" t="inlineStr"/>
       <c r="O734" t="inlineStr"/>
       <c r="P734" t="inlineStr"/>
@@ -51493,32 +51047,24 @@
         <v>1</v>
       </c>
       <c r="E736" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
           <t>BO_1971_00915</t>
         </is>
       </c>
-      <c r="G736" s="2" t="inlineStr">
+      <c r="G736" t="inlineStr">
         <is>
           <t>BR</t>
         </is>
       </c>
       <c r="H736" t="inlineStr"/>
       <c r="I736" t="inlineStr"/>
-      <c r="J736" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+      <c r="J736" t="inlineStr"/>
       <c r="K736" t="inlineStr"/>
       <c r="L736" t="inlineStr"/>
-      <c r="M736" t="inlineStr">
-        <is>
-          <t>BR</t>
-        </is>
-      </c>
+      <c r="M736" t="inlineStr"/>
       <c r="N736" t="inlineStr"/>
       <c r="O736" t="inlineStr"/>
       <c r="P736" t="inlineStr"/>
@@ -51785,14 +51331,14 @@
         <v>2</v>
       </c>
       <c r="E740" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
           <t>BO_1975_00158</t>
         </is>
       </c>
-      <c r="G740" s="2" t="inlineStr">
+      <c r="G740" t="inlineStr">
         <is>
           <t>BJ</t>
         </is>
@@ -51803,11 +51349,7 @@
         </is>
       </c>
       <c r="I740" t="inlineStr"/>
-      <c r="J740" t="inlineStr">
-        <is>
-          <t>BJ</t>
-        </is>
-      </c>
+      <c r="J740" t="inlineStr"/>
       <c r="K740" t="inlineStr">
         <is>
           <t>Coord Territorial 1 Cuauhtemoc (Col San Simon Tolnahuac)</t>
@@ -51816,7 +51358,7 @@
       <c r="L740" t="inlineStr"/>
       <c r="M740" t="inlineStr">
         <is>
-          <t>BJ+Coord Territorial 1 Cuauhtemoc (Col San Simon Tolnahuac)</t>
+          <t>Coord Territorial 1 Cuauhtemoc (Col San Simon Tolnahuac)</t>
         </is>
       </c>
       <c r="N740" t="inlineStr"/>
@@ -52317,13 +51859,13 @@
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="L747" t="inlineStr"/>
       <c r="M747" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)+Hospital Xoco (Col General Anaya)</t>
+          <t>Hospital Xoco (Col General Anaya)+Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N747" t="inlineStr">
@@ -52446,32 +51988,24 @@
         <v>1</v>
       </c>
       <c r="E749" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
           <t>BO_1971_01660</t>
         </is>
       </c>
-      <c r="G749" s="2" t="inlineStr">
+      <c r="G749" t="inlineStr">
         <is>
           <t>HT</t>
         </is>
       </c>
       <c r="H749" t="inlineStr"/>
       <c r="I749" t="inlineStr"/>
-      <c r="J749" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
+      <c r="J749" t="inlineStr"/>
       <c r="K749" t="inlineStr"/>
       <c r="L749" t="inlineStr"/>
-      <c r="M749" t="inlineStr">
-        <is>
-          <t>HT</t>
-        </is>
-      </c>
+      <c r="M749" t="inlineStr"/>
       <c r="N749" t="inlineStr"/>
       <c r="O749" t="inlineStr"/>
       <c r="P749" t="inlineStr"/>
@@ -52860,32 +52394,24 @@
         <v>1</v>
       </c>
       <c r="E755" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
           <t>BO_1976_05771</t>
         </is>
       </c>
-      <c r="G755" s="2" t="inlineStr">
+      <c r="G755" t="inlineStr">
         <is>
           <t>CA-3</t>
         </is>
       </c>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr"/>
-      <c r="J755" t="inlineStr">
-        <is>
-          <t>CA-3</t>
-        </is>
-      </c>
+      <c r="J755" t="inlineStr"/>
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr"/>
-      <c r="M755" t="inlineStr">
-        <is>
-          <t>CA-3</t>
-        </is>
-      </c>
+      <c r="M755" t="inlineStr"/>
       <c r="N755" t="inlineStr"/>
       <c r="O755" t="inlineStr"/>
       <c r="P755" t="inlineStr"/>
@@ -52998,32 +52524,24 @@
         <v>1</v>
       </c>
       <c r="E757" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
           <t>BO_1972_04581</t>
         </is>
       </c>
-      <c r="G757" s="2" t="inlineStr">
+      <c r="G757" t="inlineStr">
         <is>
           <t>Grupo 1o</t>
         </is>
       </c>
       <c r="H757" t="inlineStr"/>
       <c r="I757" t="inlineStr"/>
-      <c r="J757" t="inlineStr">
-        <is>
-          <t>Grupo 1o</t>
-        </is>
-      </c>
+      <c r="J757" t="inlineStr"/>
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr"/>
-      <c r="M757" t="inlineStr">
-        <is>
-          <t>Grupo 1o</t>
-        </is>
-      </c>
+      <c r="M757" t="inlineStr"/>
       <c r="N757" t="inlineStr"/>
       <c r="O757" t="inlineStr"/>
       <c r="P757" t="inlineStr"/>
@@ -53051,32 +52569,24 @@
         <v>1</v>
       </c>
       <c r="E758" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
           <t>BO_1973_05445</t>
         </is>
       </c>
-      <c r="G758" s="2" t="inlineStr">
+      <c r="G758" t="inlineStr">
         <is>
           <t>Gpo. 4-</t>
         </is>
       </c>
       <c r="H758" t="inlineStr"/>
       <c r="I758" t="inlineStr"/>
-      <c r="J758" t="inlineStr">
-        <is>
-          <t>Gpo. 4-</t>
-        </is>
-      </c>
+      <c r="J758" t="inlineStr"/>
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr"/>
-      <c r="M758" t="inlineStr">
-        <is>
-          <t>Gpo. 4-</t>
-        </is>
-      </c>
+      <c r="M758" t="inlineStr"/>
       <c r="N758" t="inlineStr"/>
       <c r="O758" t="inlineStr"/>
       <c r="P758" t="inlineStr"/>
@@ -53104,32 +52614,24 @@
         <v>1</v>
       </c>
       <c r="E759" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
           <t>BO_1975_06859</t>
         </is>
       </c>
-      <c r="G759" s="2" t="inlineStr">
+      <c r="G759" t="inlineStr">
         <is>
           <t>GH-1</t>
         </is>
       </c>
       <c r="H759" t="inlineStr"/>
       <c r="I759" t="inlineStr"/>
-      <c r="J759" t="inlineStr">
-        <is>
-          <t>GH-1</t>
-        </is>
-      </c>
+      <c r="J759" t="inlineStr"/>
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr"/>
-      <c r="M759" t="inlineStr">
-        <is>
-          <t>GH-1</t>
-        </is>
-      </c>
+      <c r="M759" t="inlineStr"/>
       <c r="N759" t="inlineStr"/>
       <c r="O759" t="inlineStr"/>
       <c r="P759" t="inlineStr"/>
@@ -53226,32 +52728,24 @@
         <v>1</v>
       </c>
       <c r="E761" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
           <t>BO_1976_01991</t>
         </is>
       </c>
-      <c r="G761" s="2" t="inlineStr">
+      <c r="G761" t="inlineStr">
         <is>
           <t>GAM-6</t>
         </is>
       </c>
       <c r="H761" t="inlineStr"/>
       <c r="I761" t="inlineStr"/>
-      <c r="J761" t="inlineStr">
-        <is>
-          <t>GAM-6</t>
-        </is>
-      </c>
+      <c r="J761" t="inlineStr"/>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr"/>
-      <c r="M761" t="inlineStr">
-        <is>
-          <t>GAM-6</t>
-        </is>
-      </c>
+      <c r="M761" t="inlineStr"/>
       <c r="N761" t="inlineStr"/>
       <c r="O761" t="inlineStr"/>
       <c r="P761" t="inlineStr"/>
@@ -53486,32 +52980,24 @@
         <v>1</v>
       </c>
       <c r="E765" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
           <t>BO_1977_00434</t>
         </is>
       </c>
-      <c r="G765" s="2" t="inlineStr">
+      <c r="G765" t="inlineStr">
         <is>
           <t>EMGM</t>
         </is>
       </c>
       <c r="H765" t="inlineStr"/>
       <c r="I765" t="inlineStr"/>
-      <c r="J765" t="inlineStr">
-        <is>
-          <t>EMGM</t>
-        </is>
-      </c>
+      <c r="J765" t="inlineStr"/>
       <c r="K765" t="inlineStr"/>
       <c r="L765" t="inlineStr"/>
-      <c r="M765" t="inlineStr">
-        <is>
-          <t>EMGM</t>
-        </is>
-      </c>
+      <c r="M765" t="inlineStr"/>
       <c r="N765" t="inlineStr"/>
       <c r="O765" t="inlineStr"/>
       <c r="P765" t="inlineStr"/>
@@ -53539,14 +53025,14 @@
         <v>2</v>
       </c>
       <c r="E766" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
           <t>BO_1975_00050</t>
         </is>
       </c>
-      <c r="G766" s="2" t="inlineStr">
+      <c r="G766" t="inlineStr">
         <is>
           <t>EAM</t>
         </is>
@@ -53557,11 +53043,7 @@
         </is>
       </c>
       <c r="I766" t="inlineStr"/>
-      <c r="J766" t="inlineStr">
-        <is>
-          <t>EAM</t>
-        </is>
-      </c>
+      <c r="J766" t="inlineStr"/>
       <c r="K766" t="inlineStr">
         <is>
           <t>Hospital la Villa (Col Granjas Modernas)</t>
@@ -53570,7 +53052,7 @@
       <c r="L766" t="inlineStr"/>
       <c r="M766" t="inlineStr">
         <is>
-          <t>EAM+Hospital la Villa (Col Granjas Modernas)</t>
+          <t>Hospital la Villa (Col Granjas Modernas)</t>
         </is>
       </c>
       <c r="N766" t="inlineStr"/>
@@ -53685,32 +53167,24 @@
         <v>1</v>
       </c>
       <c r="E768" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
           <t>BO_1973_04248</t>
         </is>
       </c>
-      <c r="G768" s="2" t="inlineStr">
+      <c r="G768" t="inlineStr">
         <is>
           <t>Disp.</t>
         </is>
       </c>
       <c r="H768" t="inlineStr"/>
       <c r="I768" t="inlineStr"/>
-      <c r="J768" t="inlineStr">
-        <is>
-          <t>Disp.</t>
-        </is>
-      </c>
+      <c r="J768" t="inlineStr"/>
       <c r="K768" t="inlineStr"/>
       <c r="L768" t="inlineStr"/>
-      <c r="M768" t="inlineStr">
-        <is>
-          <t>Disp.</t>
-        </is>
-      </c>
+      <c r="M768" t="inlineStr"/>
       <c r="N768" t="inlineStr"/>
       <c r="O768" t="inlineStr"/>
       <c r="P768" t="inlineStr"/>
@@ -54492,14 +53966,14 @@
       <c r="I779" t="inlineStr"/>
       <c r="J779" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K779" t="inlineStr"/>
       <c r="L779" t="inlineStr"/>
       <c r="M779" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N779" t="inlineStr">
@@ -54983,32 +54457,24 @@
         <v>1</v>
       </c>
       <c r="E786" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
           <t>BO_1974_01630</t>
         </is>
       </c>
-      <c r="G786" s="2" t="inlineStr">
+      <c r="G786" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
       <c r="H786" t="inlineStr"/>
       <c r="I786" t="inlineStr"/>
-      <c r="J786" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+      <c r="J786" t="inlineStr"/>
       <c r="K786" t="inlineStr"/>
       <c r="L786" t="inlineStr"/>
-      <c r="M786" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
+      <c r="M786" t="inlineStr"/>
       <c r="N786" t="inlineStr"/>
       <c r="O786" t="inlineStr"/>
       <c r="P786" t="inlineStr"/>
@@ -55052,14 +54518,14 @@
       <c r="I787" t="inlineStr"/>
       <c r="J787" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K787" t="inlineStr"/>
       <c r="L787" t="inlineStr"/>
       <c r="M787" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N787" t="inlineStr">
@@ -55174,32 +54640,24 @@
         <v>1</v>
       </c>
       <c r="E789" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
           <t>BO_1968_03002</t>
         </is>
       </c>
-      <c r="G789" s="2" t="inlineStr">
+      <c r="G789" t="inlineStr">
         <is>
           <t>HEV</t>
         </is>
       </c>
       <c r="H789" t="inlineStr"/>
       <c r="I789" t="inlineStr"/>
-      <c r="J789" t="inlineStr">
-        <is>
-          <t>HEV</t>
-        </is>
-      </c>
+      <c r="J789" t="inlineStr"/>
       <c r="K789" t="inlineStr"/>
       <c r="L789" t="inlineStr"/>
-      <c r="M789" t="inlineStr">
-        <is>
-          <t>HEV</t>
-        </is>
-      </c>
+      <c r="M789" t="inlineStr"/>
       <c r="N789" t="inlineStr"/>
       <c r="O789" t="inlineStr"/>
       <c r="P789" t="inlineStr"/>
@@ -56002,32 +55460,24 @@
         <v>1</v>
       </c>
       <c r="E801" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
           <t>BO_1979_04269</t>
         </is>
       </c>
-      <c r="G801" s="2" t="inlineStr">
+      <c r="G801" t="inlineStr">
         <is>
           <t>52a</t>
         </is>
       </c>
       <c r="H801" t="inlineStr"/>
       <c r="I801" t="inlineStr"/>
-      <c r="J801" t="inlineStr">
-        <is>
-          <t>52a</t>
-        </is>
-      </c>
+      <c r="J801" t="inlineStr"/>
       <c r="K801" t="inlineStr"/>
       <c r="L801" t="inlineStr"/>
-      <c r="M801" t="inlineStr">
-        <is>
-          <t>52a</t>
-        </is>
-      </c>
+      <c r="M801" t="inlineStr"/>
       <c r="N801" t="inlineStr"/>
       <c r="O801" t="inlineStr"/>
       <c r="P801" t="inlineStr"/>
@@ -56363,7 +55813,7 @@
         <v>2</v>
       </c>
       <c r="E806" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -56375,7 +55825,7 @@
           <t>CUH-6</t>
         </is>
       </c>
-      <c r="H806" s="2" t="inlineStr">
+      <c r="H806" t="inlineStr">
         <is>
           <t>Grupo 2</t>
         </is>
@@ -56386,15 +55836,11 @@
           <t>Coord Territorial 6 Cuauhtemoc (Col Centro)</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
+      <c r="K806" t="inlineStr"/>
       <c r="L806" t="inlineStr"/>
       <c r="M806" t="inlineStr">
         <is>
-          <t>Coord Territorial 6 Cuauhtemoc (Col Centro)+Grupo 2</t>
+          <t>Coord Territorial 6 Cuauhtemoc (Col Centro)</t>
         </is>
       </c>
       <c r="N806" t="inlineStr">
@@ -56870,32 +56316,24 @@
         <v>1</v>
       </c>
       <c r="E813" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
           <t>BO_1975_01289</t>
         </is>
       </c>
-      <c r="G813" s="2" t="inlineStr">
+      <c r="G813" t="inlineStr">
         <is>
           <t>CU-4</t>
         </is>
       </c>
       <c r="H813" t="inlineStr"/>
       <c r="I813" t="inlineStr"/>
-      <c r="J813" t="inlineStr">
-        <is>
-          <t>CU-4</t>
-        </is>
-      </c>
+      <c r="J813" t="inlineStr"/>
       <c r="K813" t="inlineStr"/>
       <c r="L813" t="inlineStr"/>
-      <c r="M813" t="inlineStr">
-        <is>
-          <t>CU-4</t>
-        </is>
-      </c>
+      <c r="M813" t="inlineStr"/>
       <c r="N813" t="inlineStr"/>
       <c r="O813" t="inlineStr"/>
       <c r="P813" t="inlineStr"/>
@@ -57109,14 +56547,14 @@
         <v>2</v>
       </c>
       <c r="E816" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
           <t>BO_1975_02438</t>
         </is>
       </c>
-      <c r="G816" s="2" t="inlineStr">
+      <c r="G816" t="inlineStr">
         <is>
           <t>CD-2</t>
         </is>
@@ -57127,11 +56565,7 @@
         </is>
       </c>
       <c r="I816" t="inlineStr"/>
-      <c r="J816" t="inlineStr">
-        <is>
-          <t>CD-2</t>
-        </is>
-      </c>
+      <c r="J816" t="inlineStr"/>
       <c r="K816" t="inlineStr">
         <is>
           <t>Hospital la Villa (Col Granjas Modernas)</t>
@@ -57140,7 +56574,7 @@
       <c r="L816" t="inlineStr"/>
       <c r="M816" t="inlineStr">
         <is>
-          <t>CD-2+Hospital la Villa (Col Granjas Modernas)</t>
+          <t>Hospital la Villa (Col Granjas Modernas)</t>
         </is>
       </c>
       <c r="N816" t="inlineStr"/>
@@ -57186,32 +56620,24 @@
         <v>1</v>
       </c>
       <c r="E817" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
           <t>BO_1980_05665</t>
         </is>
       </c>
-      <c r="G817" s="2" t="inlineStr">
+      <c r="G817" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
       <c r="H817" t="inlineStr"/>
       <c r="I817" t="inlineStr"/>
-      <c r="J817" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
+      <c r="J817" t="inlineStr"/>
       <c r="K817" t="inlineStr"/>
       <c r="L817" t="inlineStr"/>
-      <c r="M817" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
+      <c r="M817" t="inlineStr"/>
       <c r="N817" t="inlineStr"/>
       <c r="O817" t="inlineStr"/>
       <c r="P817" t="inlineStr"/>
@@ -57255,14 +56681,14 @@
       <c r="I818" t="inlineStr"/>
       <c r="J818" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K818" t="inlineStr"/>
       <c r="L818" t="inlineStr"/>
       <c r="M818" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N818" t="inlineStr">
@@ -57333,13 +56759,13 @@
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="L819" t="inlineStr"/>
       <c r="M819" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)+Hospital la Villa (Col Granjas Modernas)</t>
+          <t>Hospital la Villa (Col Granjas Modernas)+Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N819" t="inlineStr">
@@ -57409,14 +56835,14 @@
       <c r="I820" t="inlineStr"/>
       <c r="J820" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="K820" t="inlineStr"/>
       <c r="L820" t="inlineStr"/>
       <c r="M820" t="inlineStr">
         <is>
-          <t>Agencia del Ministerio Publico Homicidios y Secuestros (Col Guerrero)</t>
+          <t>Sistema de Transporte Colectivo Metro Zarco y Violeta (Col Guerrero)</t>
         </is>
       </c>
       <c r="N820" t="inlineStr">
@@ -57462,32 +56888,24 @@
         <v>1</v>
       </c>
       <c r="E821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
           <t>BO_1979_00009</t>
         </is>
       </c>
-      <c r="G821" s="2" t="inlineStr">
+      <c r="G821" t="inlineStr">
         <is>
           <t>81a</t>
         </is>
       </c>
       <c r="H821" t="inlineStr"/>
       <c r="I821" t="inlineStr"/>
-      <c r="J821" t="inlineStr">
-        <is>
-          <t>81a</t>
-        </is>
-      </c>
+      <c r="J821" t="inlineStr"/>
       <c r="K821" t="inlineStr"/>
       <c r="L821" t="inlineStr"/>
-      <c r="M821" t="inlineStr">
-        <is>
-          <t>81a</t>
-        </is>
-      </c>
+      <c r="M821" t="inlineStr"/>
       <c r="N821" t="inlineStr"/>
       <c r="O821" t="inlineStr"/>
       <c r="P821" t="inlineStr"/>
@@ -57823,14 +57241,14 @@
         <v>2</v>
       </c>
       <c r="E826" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
           <t>BO_1975_01535</t>
         </is>
       </c>
-      <c r="G826" s="2" t="inlineStr">
+      <c r="G826" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -57841,11 +57259,7 @@
         </is>
       </c>
       <c r="I826" t="inlineStr"/>
-      <c r="J826" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+      <c r="J826" t="inlineStr"/>
       <c r="K826" t="inlineStr">
         <is>
           <t>Hospital Xoco (Col General Anaya)</t>
@@ -57854,7 +57268,7 @@
       <c r="L826" t="inlineStr"/>
       <c r="M826" t="inlineStr">
         <is>
-          <t>C1+Hospital Xoco (Col General Anaya)</t>
+          <t>Hospital Xoco (Col General Anaya)</t>
         </is>
       </c>
       <c r="N826" t="inlineStr"/>
@@ -57900,14 +57314,14 @@
         <v>2</v>
       </c>
       <c r="E827" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
           <t>BO_1975_06841</t>
         </is>
       </c>
-      <c r="G827" s="2" t="inlineStr">
+      <c r="G827" t="inlineStr">
         <is>
           <t>C1</t>
         </is>
@@ -57918,11 +57332,7 @@
         </is>
       </c>
       <c r="I827" t="inlineStr"/>
-      <c r="J827" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
+      <c r="J827" t="inlineStr"/>
       <c r="K827" t="inlineStr">
         <is>
           <t>Hospital Xoco (Col General Anaya)</t>
@@ -57931,7 +57341,7 @@
       <c r="L827" t="inlineStr"/>
       <c r="M827" t="inlineStr">
         <is>
-          <t>C1+Hospital Xoco (Col General Anaya)</t>
+          <t>Hospital Xoco (Col General Anaya)</t>
         </is>
       </c>
       <c r="N827" t="inlineStr"/>
@@ -58062,32 +57472,24 @@
         <v>1</v>
       </c>
       <c r="E829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
           <t>BO_1976_05499</t>
         </is>
       </c>
-      <c r="G829" s="2" t="inlineStr">
+      <c r="G829" t="inlineStr">
         <is>
           <t>CH-7</t>
         </is>
       </c>
       <c r="H829" t="inlineStr"/>
       <c r="I829" t="inlineStr"/>
-      <c r="J829" t="inlineStr">
-        <is>
-          <t>CH-7</t>
-        </is>
-      </c>
+      <c r="J829" t="inlineStr"/>
       <c r="K829" t="inlineStr"/>
       <c r="L829" t="inlineStr"/>
-      <c r="M829" t="inlineStr">
-        <is>
-          <t>CH-7</t>
-        </is>
-      </c>
+      <c r="M829" t="inlineStr"/>
       <c r="N829" t="inlineStr"/>
       <c r="O829" t="inlineStr"/>
       <c r="P829" t="inlineStr"/>
@@ -58641,32 +58043,24 @@
         <v>1</v>
       </c>
       <c r="E836" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
           <t>BO_1976_01215</t>
         </is>
       </c>
-      <c r="G836" s="2" t="inlineStr">
+      <c r="G836" t="inlineStr">
         <is>
           <t>GAM-6</t>
         </is>
       </c>
       <c r="H836" t="inlineStr"/>
       <c r="I836" t="inlineStr"/>
-      <c r="J836" t="inlineStr">
-        <is>
-          <t>GAM-6</t>
-        </is>
-      </c>
+      <c r="J836" t="inlineStr"/>
       <c r="K836" t="inlineStr"/>
       <c r="L836" t="inlineStr"/>
-      <c r="M836" t="inlineStr">
-        <is>
-          <t>GAM-6</t>
-        </is>
-      </c>
+      <c r="M836" t="inlineStr"/>
       <c r="N836" t="inlineStr"/>
       <c r="O836" t="inlineStr"/>
       <c r="P836" t="inlineStr"/>
@@ -58986,32 +58380,24 @@
         <v>1</v>
       </c>
       <c r="E841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
           <t>BO_1981_02941</t>
         </is>
       </c>
-      <c r="G841" s="2" t="inlineStr">
+      <c r="G841" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
       <c r="H841" t="inlineStr"/>
       <c r="I841" t="inlineStr"/>
-      <c r="J841" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
+      <c r="J841" t="inlineStr"/>
       <c r="K841" t="inlineStr"/>
       <c r="L841" t="inlineStr"/>
-      <c r="M841" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
+      <c r="M841" t="inlineStr"/>
       <c r="N841" t="inlineStr"/>
       <c r="O841" t="inlineStr"/>
       <c r="P841" t="inlineStr"/>
@@ -59177,32 +58563,24 @@
         <v>1</v>
       </c>
       <c r="E844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
           <t>BO_1979_00087</t>
         </is>
       </c>
-      <c r="G844" s="2" t="inlineStr">
+      <c r="G844" t="inlineStr">
         <is>
           <t>364</t>
         </is>
       </c>
       <c r="H844" t="inlineStr"/>
       <c r="I844" t="inlineStr"/>
-      <c r="J844" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="J844" t="inlineStr"/>
       <c r="K844" t="inlineStr"/>
       <c r="L844" t="inlineStr"/>
-      <c r="M844" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
+      <c r="M844" t="inlineStr"/>
       <c r="N844" t="inlineStr"/>
       <c r="O844" t="inlineStr"/>
       <c r="P844" t="inlineStr"/>
@@ -59315,40 +58693,28 @@
         <v>2</v>
       </c>
       <c r="E846" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
           <t>BO_1973_04664</t>
         </is>
       </c>
-      <c r="G846" s="2" t="inlineStr">
+      <c r="G846" t="inlineStr">
         <is>
           <t>45a</t>
         </is>
       </c>
-      <c r="H846" s="2" t="inlineStr">
+      <c r="H846" t="inlineStr">
         <is>
           <t>COY</t>
         </is>
       </c>
       <c r="I846" t="inlineStr"/>
-      <c r="J846" t="inlineStr">
-        <is>
-          <t>45a</t>
-        </is>
-      </c>
-      <c r="K846" t="inlineStr">
-        <is>
-          <t>COY</t>
-        </is>
-      </c>
+      <c r="J846" t="inlineStr"/>
+      <c r="K846" t="inlineStr"/>
       <c r="L846" t="inlineStr"/>
-      <c r="M846" t="inlineStr">
-        <is>
-          <t>45a+COY</t>
-        </is>
-      </c>
+      <c r="M846" t="inlineStr"/>
       <c r="N846" t="inlineStr"/>
       <c r="O846" t="inlineStr"/>
       <c r="P846" t="inlineStr"/>
@@ -60045,32 +59411,24 @@
         <v>1</v>
       </c>
       <c r="E856" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
           <t>BO_1973_03504</t>
         </is>
       </c>
-      <c r="G856" s="2" t="inlineStr">
+      <c r="G856" t="inlineStr">
         <is>
           <t>CUH</t>
         </is>
       </c>
       <c r="H856" t="inlineStr"/>
       <c r="I856" t="inlineStr"/>
-      <c r="J856" t="inlineStr">
-        <is>
-          <t>CUH</t>
-        </is>
-      </c>
+      <c r="J856" t="inlineStr"/>
       <c r="K856" t="inlineStr"/>
       <c r="L856" t="inlineStr"/>
-      <c r="M856" t="inlineStr">
-        <is>
-          <t>CUH</t>
-        </is>
-      </c>
+      <c r="M856" t="inlineStr"/>
       <c r="N856" t="inlineStr"/>
       <c r="O856" t="inlineStr"/>
       <c r="P856" t="inlineStr"/>
@@ -60098,32 +59456,24 @@
         <v>1</v>
       </c>
       <c r="E857" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
           <t>BO_1971_01005</t>
         </is>
       </c>
-      <c r="G857" s="2" t="inlineStr">
+      <c r="G857" t="inlineStr">
         <is>
           <t>CUJ</t>
         </is>
       </c>
       <c r="H857" t="inlineStr"/>
       <c r="I857" t="inlineStr"/>
-      <c r="J857" t="inlineStr">
-        <is>
-          <t>CUJ</t>
-        </is>
-      </c>
+      <c r="J857" t="inlineStr"/>
       <c r="K857" t="inlineStr"/>
       <c r="L857" t="inlineStr"/>
-      <c r="M857" t="inlineStr">
-        <is>
-          <t>CUJ</t>
-        </is>
-      </c>
+      <c r="M857" t="inlineStr"/>
       <c r="N857" t="inlineStr"/>
       <c r="O857" t="inlineStr"/>
       <c r="P857" t="inlineStr"/>
@@ -60151,14 +59501,14 @@
         <v>2</v>
       </c>
       <c r="E858" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
           <t>BO_1971_01749</t>
         </is>
       </c>
-      <c r="G858" s="2" t="inlineStr">
+      <c r="G858" t="inlineStr">
         <is>
           <t>COY</t>
         </is>
@@ -60169,11 +59519,7 @@
         </is>
       </c>
       <c r="I858" t="inlineStr"/>
-      <c r="J858" t="inlineStr">
-        <is>
-          <t>COY</t>
-        </is>
-      </c>
+      <c r="J858" t="inlineStr"/>
       <c r="K858" t="inlineStr">
         <is>
           <t>Hospital Xoco (Col General Anaya)</t>
@@ -60182,7 +59528,7 @@
       <c r="L858" t="inlineStr"/>
       <c r="M858" t="inlineStr">
         <is>
-          <t>COY+Hospital Xoco (Col General Anaya)</t>
+          <t>Hospital Xoco (Col General Anaya)</t>
         </is>
       </c>
       <c r="N858" t="inlineStr"/>
@@ -60297,32 +59643,24 @@
         <v>1</v>
       </c>
       <c r="E860" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
           <t>BO_1978_00606</t>
         </is>
       </c>
-      <c r="G860" s="2" t="inlineStr">
+      <c r="G860" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
       <c r="H860" t="inlineStr"/>
       <c r="I860" t="inlineStr"/>
-      <c r="J860" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
+      <c r="J860" t="inlineStr"/>
       <c r="K860" t="inlineStr"/>
       <c r="L860" t="inlineStr"/>
-      <c r="M860" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
+      <c r="M860" t="inlineStr"/>
       <c r="N860" t="inlineStr"/>
       <c r="O860" t="inlineStr"/>
       <c r="P860" t="inlineStr"/>
